--- a/results/Int All Data -0.1/Rando_8_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_8_permute.xlsx
@@ -440,1153 +440,1153 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7439720582807262</v>
+        <v>0.7580009474994007</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7443644714361275</v>
+        <v>0.7457628892262849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7460506588735792</v>
+        <v>0.7561758695875525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7386157376225756</v>
+        <v>0.7576085343439993</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7386157376225756</v>
+        <v>0.7540791942069354</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7419619516204523</v>
+        <v>0.7477106854340042</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7437527825660111</v>
+        <v>0.7441551844199135</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7445737584523415</v>
+        <v>0.7449761603062439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7422777847540116</v>
+        <v>0.7442859888050473</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7485416500188358</v>
+        <v>0.7476926106462403</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7505336818913457</v>
+        <v>0.7459017797006815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7434750016172178</v>
+        <v>0.7501736130929957</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7459298431869466</v>
+        <v>0.7523749319817197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7404346320543994</v>
+        <v>0.7584375963195926</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7377785895577195</v>
+        <v>0.757747424818396</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7365994474822772</v>
+        <v>0.7508195489294018</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7380844339927777</v>
+        <v>0.7540349585421446</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7420242620730069</v>
+        <v>0.7532482296221037</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.746418813761192</v>
+        <v>0.760717397839397</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7439577887114388</v>
+        <v>0.760717397839397</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7437746625722516</v>
+        <v>0.7638624109103225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7414506253876566</v>
+        <v>0.7594155374680838</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7424728022009384</v>
+        <v>0.7556588355270417</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7402191615581608</v>
+        <v>0.7576770282765786</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7398609953690491</v>
+        <v>0.760158030723334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7390219446949546</v>
+        <v>0.7559123582080465</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7463683946163768</v>
+        <v>0.7562705243971583</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7469539226094666</v>
+        <v>0.757397344718547</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7481592255619356</v>
+        <v>0.7490025571068163</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7522740936920893</v>
+        <v>0.7466523590451946</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.743704266030434</v>
+        <v>0.7480850238016417</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7429879336522106</v>
+        <v>0.7474210131774717</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7577512300368725</v>
+        <v>0.7467308416762748</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7570348976586491</v>
+        <v>0.7446341662956579</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.738732272438422</v>
+        <v>0.7339415023763589</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.738732272438422</v>
+        <v>0.7339415023763589</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7312892650981556</v>
+        <v>0.7272933100453962</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.733665624036804</v>
+        <v>0.7247076640905338</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7379212852505926</v>
+        <v>0.7232749993340868</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7380782505127532</v>
+        <v>0.7232749993340868</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7410401374444914</v>
+        <v>0.7315651434377105</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7491371667104267</v>
+        <v>0.731949470503849</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7423581699943302</v>
+        <v>0.7298789560002588</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7370460850009704</v>
+        <v>0.7266816211752798</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7370460850009704</v>
+        <v>0.7205927959603801</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7386799506843685</v>
+        <v>0.7165302495842799</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7384706636681545</v>
+        <v>0.7154557510169446</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7486039604713904</v>
+        <v>0.7193170964660935</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7402534085244504</v>
+        <v>0.7200334288443171</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7394324326381199</v>
+        <v>0.7135602765632789</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7302689908941122</v>
+        <v>0.7185042066690259</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7360781325509804</v>
+        <v>0.71453821771177</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7366898214210968</v>
+        <v>0.7107030331396478</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7303032378604017</v>
+        <v>0.6945070719985389</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7299189107942632</v>
+        <v>0.6840679307602446</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7295869054821782</v>
+        <v>0.6891345791618626</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.742430469145386</v>
+        <v>0.6891345791618626</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.741766458521216</v>
+        <v>0.6871344612000898</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7433822494168503</v>
+        <v>0.6829411104388559</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7332670274013783</v>
+        <v>0.6756993040255406</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7375830964584832</v>
+        <v>0.6634189126968725</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7399856162741584</v>
+        <v>0.6644410895101542</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7297557620520783</v>
+        <v>0.6659160873221537</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7285223956133442</v>
+        <v>0.679107828475972</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7343496120579762</v>
+        <v>0.6853978546178229</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7441166565828377</v>
+        <v>0.6853978546178229</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7467726990795176</v>
+        <v>0.6789066275490208</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7356091393737372</v>
+        <v>0.670044749369285</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7335566996579108</v>
+        <v>0.6739403417847236</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7352167262183358</v>
+        <v>0.6739403417847236</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7348062382751706</v>
+        <v>0.6739403417847236</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7299669516775306</v>
+        <v>0.6739403417847236</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7275121101078018</v>
+        <v>0.6803269253454187</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7342649459468715</v>
+        <v>0.6683062401777797</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7344219112090321</v>
+        <v>0.6638070449814876</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7344219112090321</v>
+        <v>0.6698173875653071</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7358545759654791</v>
+        <v>0.6460918503635886</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7354964097763673</v>
+        <v>0.6426148319805781</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7366917240303352</v>
+        <v>0.6422305049144397</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7118193891102258</v>
+        <v>0.6431218773425876</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6980440225725559</v>
+        <v>0.6647507391636891</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7011628747664548</v>
+        <v>0.6311111808734499</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7019576897757585</v>
+        <v>0.6314693470625616</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6979736260307385</v>
+        <v>0.5682851212152346</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7016014261958851</v>
+        <v>0.5747321126192461</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7016014261958851</v>
+        <v>0.5837909108551468</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6585510869606579</v>
+        <v>0.5837909108551468</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6407393349239147</v>
+        <v>0.5916182452615517</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6047819229291049</v>
+        <v>0.5988338907978402</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6021620300079529</v>
+        <v>0.6005200782352919</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6021620300079529</v>
+        <v>0.6043029410533606</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6014456976297294</v>
+        <v>0.5881593016663051</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5567976422866319</v>
+        <v>0.5852235756115938</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5594798456603386</v>
+        <v>0.562300939508442</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5627737379041617</v>
+        <v>0.5691845797326454</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5594636734818129</v>
+        <v>0.580567415153141</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5419396910923641</v>
+        <v>0.5544655190127741</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.562206284698836</v>
+        <v>0.5544655190127741</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.553050929044091</v>
+        <v>0.5544655190127741</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5451108650403163</v>
+        <v>0.5539765484385286</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.548334360742322</v>
+        <v>0.5533125378143586</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5415030422721721</v>
+        <v>0.5536183822494168</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5414768813951453</v>
+        <v>0.5502117604082238</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5331686625037577</v>
+        <v>0.5502117604082238</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5331425016267309</v>
+        <v>0.5563971430419677</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5210352477387489</v>
+        <v>0.501432664756447</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5242064216867012</v>
+        <v>0.5007163323782235</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5241540999326476</v>
+        <v>0.5007163323782235</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.506271951354087</v>
+        <v>0.5007163323782235</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.506271951354087</v>
+        <v>0.5007424932552502</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.505939946042002</v>
+        <v>0.4974486010114271</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5055817798528902</v>
+        <v>0.4981387725126238</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.50483928659764</v>
+        <v>0.4981126116355971</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4997203164419685</v>
+        <v>0.5003843270661386</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5000261608770268</v>
+        <v>0.5003843270661386</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1596,267 +1596,267 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5000261608770268</v>
+        <v>0.4996941555649418</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4993883111298835</v>
+        <v>0.4996941555649418</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5004628096972188</v>
+        <v>0.4996941555649418</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5007948150093038</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.500768654132277</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.500436648820192</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4997464773189953</v>
+        <v>0.499667994687915</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4997464773189953</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4997464773189953</v>
+        <v>0.5000261608770268</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4997464773189953</v>
+        <v>0.5000261608770268</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.500436648820192</v>
+        <v>0.5000261608770268</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.500436648820192</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.500104643508107</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.501100659444362</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4988289440138206</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4944082314486086</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4927743657652104</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4927743657652104</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4911928218358657</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4961205797630871</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4957885744510021</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4964264241981454</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.49867197875166</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.49867197875166</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.49933598937583</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.499667994687915</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1866,47 +1866,47 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.499667994687915</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.499667994687915</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.499667994687915</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.499667994687915</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B156" t="n">
